--- a/DATA/A098460_valuation_exog.xlsx
+++ b/DATA/A098460_valuation_exog.xlsx
@@ -396,45 +396,45 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>50728051.03929299</v>
+        <v>50392979.91983175</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>48919978.45773502</v>
+        <v>48750351.2351895</v>
       </c>
       <c r="B3">
-        <v>4.827189867737771</v>
+        <v>4.813534498063357</v>
       </c>
       <c r="C3">
-        <v>236146024.3411285</v>
+        <v>234661497.4632902</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>51126266.6063676</v>
+        <v>50445236.74655022</v>
       </c>
       <c r="B4">
-        <v>4.69361125629267</v>
+        <v>4.686698328570258</v>
       </c>
       <c r="C4">
-        <v>239966820.435867</v>
+        <v>236421606.7443879</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>50485819.02133325</v>
+        <v>49970141.35112607</v>
       </c>
       <c r="B5">
-        <v>5.422669849221707</v>
+        <v>5.394915399628814</v>
       </c>
       <c r="C5">
-        <v>273767928.6202475</v>
+        <v>269584685.0968186</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="B6">
-        <v>5.078471901545244</v>
+        <v>5.05745615649732</v>
       </c>
     </row>
   </sheetData>
